--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260929.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260929.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>12,693,000</t>
+          <t>3,521,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>3,521,000</t>
+          <t>12,693,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>17,752,000</t>
+          <t>55,324,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>55,324,000</t>
+          <t>17,752,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,881,000</t>
+          <t>1,973,678</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,973,678</t>
+          <t>3,881,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
